--- a/outputs/evaluation/architecture/design/v3/CF_M01/run_1/CF_M01_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/design/v3/CF_M01/run_1/CF_M01_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.75</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.8219</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.75</v>
       </c>
       <c r="D3" t="n">
+        <v>0.8136</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9729</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.75</v>
       </c>
       <c r="D4" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8873</v>
       </c>
     </row>
@@ -1224,13 +1238,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>AWS cloud services set</t>
@@ -1256,13 +1268,11 @@
           <t>CF_M01_AU07</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1283,7 +1293,6 @@
       <c r="D3" t="n">
         <v>0.7793</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1304,7 +1313,6 @@
           <t>['AU_10', 'AU_11', 'AU_12']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_30</t>
@@ -1315,7 +1323,6 @@
           <t>web socket service, database, cloud storage service</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1334,7 +1341,6 @@
           <t>CF_M01_AU27, CF_M01_AU13</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M01_AU28</t>
@@ -1365,7 +1371,6 @@
       <c r="D4" t="n">
         <v>0.7983</v>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1386,7 +1391,6 @@
           <t>['AU_06', 'AU_07', 'AU_08', 'AU_09', 'AU_10']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_26</t>
@@ -1397,7 +1401,6 @@
           <t>api gateway service, core service, analytical module service, player api service, web socket service</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1416,7 +1419,6 @@
           <t>CF_M01_AU10, CF_M01_AU11, CF_M01_AU12</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M01_AU26</t>
@@ -1472,13 +1474,11 @@
           <t>['AU_05']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>SQL database</t>
@@ -1502,13 +1502,11 @@
           <t>CF_M01_AU07</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M01_AU15</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1554,13 +1552,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Api Player</t>
@@ -1584,13 +1580,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M01_AU13</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1636,13 +1630,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Analytical module</t>
@@ -1666,13 +1658,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M01_AU12</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1693,7 +1683,6 @@
       <c r="D8" t="n">
         <v>0.923</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1714,7 +1703,6 @@
           <t>['AU_10', 'AU_22']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_27</t>
@@ -1725,7 +1713,6 @@
           <t>web socket service, player</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1744,7 +1731,6 @@
           <t>CF_M01_AU27, CF_M01_AU14</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M01_AU29</t>
@@ -1775,7 +1761,6 @@
       <c r="D9" t="n">
         <v>0.9339</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1796,7 +1781,6 @@
           <t>['AU_08', 'AU_12']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_29</t>
@@ -1807,7 +1791,6 @@
           <t>analytical module service, cloud storage service</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1826,7 +1809,6 @@
           <t>CF_M01_AU12, CF_M01_AU16, CF_M01_AU15</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M01_AU36</t>
@@ -1857,7 +1839,6 @@
       <c r="D10" t="n">
         <v>0.9396</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1878,7 +1859,6 @@
           <t>['AU_07', 'AU_11']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_28</t>
@@ -1889,7 +1869,6 @@
           <t>core service, database</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1908,7 +1887,6 @@
           <t>CF_M01_AU11, CF_M01_AU15, CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M01_AU37</t>
@@ -1964,13 +1942,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Web Socket</t>
@@ -1994,13 +1970,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M01_AU14</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2021,7 +1995,6 @@
       <c r="D12" t="n">
         <v>0.9499</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2042,7 +2015,6 @@
           <t>['AU_03', 'AU_06']</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_25</t>
@@ -2053,7 +2025,6 @@
           <t>presentation layer, api gateway service</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -2072,7 +2043,6 @@
           <t>CF_M01_AU05, CF_M01_AU10</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M01_AU25</t>
@@ -2128,13 +2098,11 @@
           <t>['AU_12']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Amazon DynamoDB</t>
@@ -2158,13 +2126,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M01_AU18</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2205,7 +2171,6 @@
           <t>43</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Architectural Pattern</t>
@@ -2216,7 +2181,6 @@
           <t>P_03</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>API Gateway</t>
@@ -2240,13 +2204,11 @@
           <t>CF_M01_P03</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M01_P04</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2287,14 +2249,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Player</t>
@@ -2313,14 +2272,11 @@
       <c r="P15" t="n">
         <v>8</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M01_AU27</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2366,13 +2322,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Amazon Athena</t>
@@ -2396,13 +2350,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M01_AU20</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2443,14 +2395,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Presentation Layer</t>
@@ -2474,13 +2423,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M01_AU05</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2526,13 +2473,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Core Service</t>
@@ -2556,13 +2501,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M01_AU11</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2608,13 +2551,11 @@
           <t>['AU_25']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2638,13 +2579,11 @@
           <t>CF_M01_AU24, CF_M01_AU25</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M01_AU03</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2690,13 +2629,11 @@
           <t>['AU_06', 'AU_07', 'AU_08', 'AU_09', 'AU_10']</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>NestJS</t>
@@ -2720,13 +2657,11 @@
           <t>CF_M01_AU02</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2767,14 +2702,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_01</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Client</t>
@@ -2798,13 +2730,11 @@
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M01_AU01</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2850,13 +2780,11 @@
           <t>['AU_04']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>API Gateway Service</t>
@@ -2880,13 +2808,11 @@
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M01_AU10</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2932,13 +2858,11 @@
           <t>['AU_12']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Amazon S3</t>
@@ -2962,13 +2886,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M01_AU17</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3014,13 +2936,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_19</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>AWS Glue</t>
@@ -3044,13 +2964,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M01_AU21</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3091,14 +3009,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Business Layer</t>
@@ -3122,13 +3037,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M01_AU06</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3174,13 +3087,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Kinesis Data Streams</t>
@@ -3206,13 +3117,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M01_AU22</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3253,14 +3162,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Client-Server</t>
@@ -3279,14 +3185,11 @@
       <c r="P27" t="n">
         <v>41</v>
       </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M01_P01</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3332,13 +3235,11 @@
           <t>['AU_13']</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
           <t>TypeScript</t>
@@ -3362,13 +3263,11 @@
           <t>CF_M01_AU33</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr">
         <is>
           <t>CF_M01_AU34</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3409,14 +3308,11 @@
           <t>41</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
           <t>Data Layer</t>
@@ -3440,13 +3336,11 @@
           <t>CF_M01_P02</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr">
         <is>
           <t>CF_M01_AU07</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3492,13 +3386,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
           <t>Kinesis Data Firehose</t>
@@ -3522,13 +3414,11 @@
           <t>CF_M01_AU16</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
       <c r="S30" t="inlineStr">
         <is>
           <t>CF_M01_AU23</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3574,13 +3464,11 @@
           <t>['AU_26']</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
           <t>TCP</t>
@@ -3604,13 +3492,11 @@
           <t>CF_M01_AU26</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
       <c r="S31" t="inlineStr">
         <is>
           <t>CF_M01_AU31</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3684,7 +3570,6 @@
           <t>Backend</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The server is the software that is responsible for processing user requests.</t>
@@ -3720,7 +3605,6 @@
           <t>AWS</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Cloud services used for infrastructure.</t>
@@ -3756,7 +3640,6 @@
           <t>Layered Architecture</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
@@ -3848,7 +3731,6 @@
           <t>Server</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>The server is the software that is responsible for processing user requests.</t>
@@ -3879,7 +3761,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>client, server</t>
@@ -3895,7 +3776,6 @@
           <t>AU_25</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>0.823</v>
       </c>
@@ -3916,7 +3796,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Communication between the two components is carried out over the internet using the HTTP protocol and the REST API model.</t>
@@ -3952,7 +3831,6 @@
           <t>Web platform interface</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
@@ -3988,7 +3866,6 @@
           <t>Waapiti Mobile Platform</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>In the case of this layer, you can see that it is made up of the interface of the web platform and the Waapiti mobile platform.</t>
@@ -4019,7 +3896,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>presentation layer, business layer</t>
@@ -4060,7 +3936,6 @@
           <t>MySQL</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>The database used is a MySQL database that is responsible for storing all the data necessary for the operation of the system.</t>
@@ -4096,7 +3971,6 @@
           <t>AWS RDS</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>This database is implemented in the RDS service [30], which is a distributed relational database service from AWS.</t>
@@ -4132,7 +4006,6 @@
           <t>Three Layers</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>The client-server model uses a 3-layer architecture, where the system is divided into 3 layers.</t>
@@ -4168,7 +4041,6 @@
           <t>Service-oriented</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Both the business layer and the data layer are divided into several different services</t>
